--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92444</v>
+        <v>92447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92447</v>
+        <v>92448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92448</v>
+        <v>92453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80483</v>
+        <v>80485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>136580151</v>
       </c>
       <c r="B72" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>136580187</v>
       </c>
       <c r="B73" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>136580191</v>
       </c>
       <c r="B74" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>136580202</v>
       </c>
       <c r="B75" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>136580152</v>
       </c>
       <c r="B77" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>136580175</v>
       </c>
       <c r="B79" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>136580210</v>
       </c>
       <c r="B80" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>136580218</v>
       </c>
       <c r="B81" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136580231</v>
       </c>
       <c r="B82" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>136580232</v>
       </c>
       <c r="B83" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>136580173</v>
       </c>
       <c r="B84" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>136580236</v>
       </c>
       <c r="B85" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>136580235</v>
       </c>
       <c r="B86" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>136580153</v>
       </c>
       <c r="B90" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>136580221</v>
       </c>
       <c r="B91" t="n">
-        <v>56570</v>
+        <v>56572</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92453</v>
+        <v>92455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92455</v>
+        <v>92457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92457</v>
+        <v>92459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99383</v>
+        <v>99384</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92460</v>
+        <v>92466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99384</v>
+        <v>99390</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92466</v>
+        <v>92470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99390</v>
+        <v>99394</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 36755-2026 artfynd.xlsx
+++ b/artfynd/A 36755-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136580197</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136580241</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136580171</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136580226</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>136580239</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>136580240</v>
       </c>
       <c r="B10" t="n">
-        <v>92470</v>
+        <v>92472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>136580145</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>136580201</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136580213</v>
       </c>
       <c r="B17" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>136580225</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>136580238</v>
       </c>
       <c r="B19" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136580143</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>136580144</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>136580147</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>136580149</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>136580156</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136580157</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>136580169</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>136580172</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>136580174</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>136580177</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>136580178</v>
       </c>
       <c r="B30" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>136580183</v>
       </c>
       <c r="B31" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>136580186</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136580189</v>
       </c>
       <c r="B33" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>136580190</v>
       </c>
       <c r="B34" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>136580192</v>
       </c>
       <c r="B35" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>136580196</v>
       </c>
       <c r="B36" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>136580198</v>
       </c>
       <c r="B37" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>136580200</v>
       </c>
       <c r="B38" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>136580237</v>
       </c>
       <c r="B39" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>136580207</v>
       </c>
       <c r="B40" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>136580160</v>
       </c>
       <c r="B48" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>136580162</v>
       </c>
       <c r="B49" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>136580166</v>
       </c>
       <c r="B50" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>136580193</v>
       </c>
       <c r="B51" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>136580214</v>
       </c>
       <c r="B52" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>136580219</v>
       </c>
       <c r="B53" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>136580223</v>
       </c>
       <c r="B54" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>136580228</v>
       </c>
       <c r="B55" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136580229</v>
       </c>
       <c r="B56" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>136580158</v>
       </c>
       <c r="B59" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136580163</v>
       </c>
       <c r="B60" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136580170</v>
       </c>
       <c r="B61" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>136580195</v>
       </c>
       <c r="B62" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>136580199</v>
       </c>
       <c r="B63" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>136580185</v>
       </c>
       <c r="B68" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>136580205</v>
       </c>
       <c r="B71" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>136580206</v>
       </c>
       <c r="B94" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>136580211</v>
       </c>
       <c r="B95" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>136580227</v>
       </c>
       <c r="B97" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>136580212</v>
       </c>
       <c r="B98" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>136580161</v>
       </c>
       <c r="B100" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>136580194</v>
       </c>
       <c r="B101" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>136580220</v>
       </c>
       <c r="B102" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>136580159</v>
       </c>
       <c r="B105" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>136580168</v>
       </c>
       <c r="B106" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>136580208</v>
       </c>
       <c r="B107" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>136580224</v>
       </c>
       <c r="B108" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
